--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487645_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487645_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3436</v>
+        <v>6.2613</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8481</v>
+        <v>3.5478</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4955</v>
+        <v>2.7135</v>
       </c>
       <c r="G2" t="n">
         <v>4.3808</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4852</v>
+        <v>0.4029</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4385</v>
+        <v>0.1382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0467</v>
+        <v>0.2647</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6136</v>
+        <v>4.6413</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7594</v>
+        <v>2.0597</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8541</v>
+        <v>2.5816</v>
       </c>
       <c r="G3" t="n">
         <v>4.9394</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3623</v>
+        <v>0.39</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8951</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.2821</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2654</v>
+        <v>2.2863</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3549</v>
+        <v>1.248</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0895</v>
+        <v>1.0383</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4164</v>
+        <v>-1.0717</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6196</v>
+        <v>-2.3291</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0359</v>
+        <v>1.2574</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9904</v>
+        <v>1.123</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0824</v>
+        <v>-0.6962</v>
       </c>
       <c r="L4" t="n">
-        <v>1.908</v>
+        <v>1.8191</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.574</v>
+        <v>-2.1946</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7019</v>
+        <v>-1.6329</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1279</v>
+        <v>-0.5617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5821</v>
+        <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2669</v>
+        <v>0.3878</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3645</v>
+        <v>0.0653</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.3225</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5762</v>
+        <v>2.1653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3471</v>
+        <v>2.2548</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2291</v>
+        <v>-0.0895</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0717</v>
+        <v>1.4164</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3291</v>
+        <v>-0.6196</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2574</v>
+        <v>2.0359</v>
       </c>
       <c r="J5" t="n">
-        <v>1.123</v>
+        <v>1.9904</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6962</v>
+        <v>0.0824</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8191</v>
+        <v>1.908</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1946</v>
+        <v>-0.574</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6329</v>
+        <v>-0.7019</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5617</v>
+        <v>0.1279</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9105</v>
+        <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3223</v>
+        <v>0.1668</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8356</v>
+        <v>0.2644</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5133</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3129</v>
+        <v>1.5399</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8732</v>
+        <v>1.7731</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5603</v>
+        <v>-0.2332</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6998</v>
@@ -922,13 +922,13 @@
         <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1813</v>
+        <v>0.0457</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0011</v>
+        <v>-0.099</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1824</v>
+        <v>0.1447</v>
       </c>
       <c r="V6" t="n">
         <v>1.2239</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0433</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0.5752</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5319</v>
+        <v>-0.6409</v>
       </c>
       <c r="G7" t="n">
         <v>0.0545</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8246</v>
+        <v>0.7156</v>
       </c>
       <c r="T7" t="n">
         <v>0.4251</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3995</v>
+        <v>0.2905</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2239</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.151</v>
+        <v>-0.0965</v>
       </c>
       <c r="E8" t="n">
         <v>0.2421</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3931</v>
+        <v>-0.3386</v>
       </c>
       <c r="G8" t="n">
         <v>0.0091</v>
@@ -1078,13 +1078,13 @@
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3299</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6756</v>
+        <v>-0.9938</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8068</v>
+        <v>-0.9069</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1312</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7039</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5209</v>
+        <v>0.2027</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2412</v>
+        <v>-0.3413</v>
       </c>
       <c r="U9" t="n">
-        <v>0.762</v>
+        <v>0.544</v>
       </c>
       <c r="V9" t="n">
         <v>1.8358</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0131</v>
+        <v>-1.2405</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2719</v>
+        <v>-0.4721</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7411</v>
+        <v>-0.7684</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8586</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3217</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3039</v>
+        <v>0.1037</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0177</v>
+        <v>-0.0095</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>B. PINTOR HENNINGSEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1264</v>
+        <v>-1.4094</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9142</v>
+        <v>-1.4561</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.0467</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2686</v>
+        <v>-0.885</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9816</v>
+        <v>-0.6476</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.713</v>
+        <v>-0.2375</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9861</v>
+        <v>-0.256</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7425</v>
+        <v>-0.2966</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2436</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2825</v>
+        <v>-0.629</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2391</v>
+        <v>-0.351</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9565</v>
+        <v>-0.2781</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.2985</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.0448</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1274</v>
+        <v>-0.1363</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8625</v>
+        <v>-0.2299</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2649</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. PINTOR HENNINGSEN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5456</v>
+        <v>-1.5357</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4561</v>
+        <v>-2.2145</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0896</v>
+        <v>0.6788</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.885</v>
+        <v>2.2686</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6476</v>
+        <v>2.9816</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2375</v>
+        <v>-0.713</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.256</v>
+        <v>1.9861</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2966</v>
+        <v>1.7425</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0406</v>
+        <v>0.2436</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.629</v>
+        <v>0.2825</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.351</v>
+        <v>1.2391</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2781</v>
+        <v>-0.9565</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3881</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>-5.0448</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2725</v>
+        <v>0.7181</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2299</v>
+        <v>0.5622</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0426</v>
+        <v>0.1559</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1969</v>
+        <v>-4.1062</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0247</v>
+        <v>-1.1248</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1722</v>
+        <v>-2.9814</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1505</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0431</v>
+        <v>0.1337</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1828</v>
+        <v>0.0827</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4477</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4464</v>
+        <v>7.446299999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>5.526299999999999</v>
+        <v>5.526300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.92</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>5.6993</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3066</v>
+        <v>2.306599999999999</v>
       </c>
       <c r="I14" t="n">
         <v>3.392200000000001</v>
@@ -1531,7 +1531,7 @@
         <v>-8.7517</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.917399999999999</v>
+        <v>-7.9174</v>
       </c>
       <c r="O14" t="n">
         <v>-0.8343</v>
@@ -1546,10 +1546,10 @@
         <v>14.5525</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1518</v>
+        <v>3.1515</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6782999999999998</v>
+        <v>0.6782999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>2.4732</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1105</v>
+        <v>3.7083</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1065</v>
+        <v>4.7071</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.996</v>
+        <v>-0.9988</v>
       </c>
       <c r="G15" t="n">
         <v>2.5857</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0857</v>
+        <v>-0.4879</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2719</v>
+        <v>-0.6713</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1862</v>
+        <v>0.1834</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3299</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6238</v>
+        <v>2.2809</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6549</v>
+        <v>1.7934</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0311</v>
+        <v>0.4875</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8734</v>
+        <v>0.3722</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5075</v>
+        <v>2.2113</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3659</v>
+        <v>-1.8391</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1272</v>
+        <v>1.3753</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9804</v>
+        <v>3.3367</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1468</v>
+        <v>-1.9614</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0006</v>
+        <v>-1.0031</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4879</v>
+        <v>-1.1254</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5127</v>
+        <v>0.1223</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2985</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1106</v>
+        <v>-0.5271</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2157</v>
+        <v>-0.4475</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8948</v>
+        <v>-0.0796</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9418</v>
+        <v>1.2716</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4745</v>
+        <v>1.12</v>
       </c>
       <c r="E17" t="n">
-        <v>1.393</v>
+        <v>1.4537</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0815</v>
+        <v>-0.3337</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3722</v>
+        <v>-0.8734</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2113</v>
+        <v>-0.5075</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8391</v>
+        <v>-0.3659</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3753</v>
+        <v>2.1272</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3367</v>
+        <v>0.9804</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9614</v>
+        <v>1.1468</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0031</v>
+        <v>-3.0006</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1254</v>
+        <v>-1.4879</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1223</v>
+        <v>-1.5127</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1344</v>
+        <v>3.2985</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3336</v>
+        <v>0.6068</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>0.0145</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4856</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2716</v>
+        <v>-0.9418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8358</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.49</v>
+        <v>0.9735</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1043</v>
+        <v>1.9573</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3857</v>
+        <v>-0.9837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8115</v>
+        <v>0.3441</v>
       </c>
       <c r="H18" t="n">
-        <v>2.629</v>
+        <v>0.5009</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8175</v>
+        <v>-0.1568</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3042</v>
+        <v>1.6428</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8269</v>
+        <v>2.1833</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.5405</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4927</v>
+        <v>-1.2987</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1979</v>
+        <v>-1.6824</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2948</v>
+        <v>0.3837</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5453</v>
+        <v>-0.5944</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2894</v>
+        <v>-0.1929</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2559</v>
+        <v>-0.4015</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3551</v>
+        <v>0.499</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5569</v>
+        <v>0.0042</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2018</v>
+        <v>0.4947</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3441</v>
+        <v>1.8115</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5009</v>
+        <v>2.629</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1568</v>
+        <v>-0.8175</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6428</v>
+        <v>3.3042</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1833</v>
+        <v>3.8269</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5405</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2987</v>
+        <v>-1.4927</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6824</v>
+        <v>-1.1979</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3837</v>
+        <v>-0.2948</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2129</v>
+        <v>-0.5364</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5933</v>
+        <v>-0.3895</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.1469</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.153</v>
+        <v>-1.5268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5299</v>
+        <v>-1.8456</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6829</v>
+        <v>0.3188</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.221</v>
+        <v>0.2043</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3106</v>
+        <v>-0.0626</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9104</v>
+        <v>0.2669</v>
       </c>
       <c r="J20" t="n">
-        <v>0.226</v>
+        <v>0.0824</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1854</v>
+        <v>0.0824</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4469</v>
+        <v>0.1219</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.496</v>
+        <v>-0.145</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.951</v>
+        <v>0.2669</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9702</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3217</v>
+        <v>0.0151</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3039</v>
+        <v>0.0123</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0177</v>
+        <v>0.0028</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6086</v>
+        <v>-1.5807</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8456</v>
+        <v>0.1295</v>
       </c>
       <c r="F21" t="n">
-        <v>0.237</v>
+        <v>-1.7102</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2043</v>
+        <v>-1.221</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0626</v>
+        <v>-0.3106</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2669</v>
+        <v>-0.9104</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0824</v>
+        <v>0.226</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0824</v>
+        <v>0.1854</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1219</v>
+        <v>-1.4469</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.145</v>
+        <v>-0.496</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2669</v>
+        <v>-0.951</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.106</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0123</v>
+        <v>-0.0965</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.079</v>
+        <v>-0.0095</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7863</v>
+        <v>-1.6317</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.5536</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1325</v>
+        <v>-1.078</v>
       </c>
       <c r="G22" t="n">
         <v>-1.18</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6063</v>
+        <v>-0.4517</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1088</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4975</v>
+        <v>-0.443</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9281</v>
+        <v>-2.7218</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5267</v>
+        <v>-3.4266</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5986</v>
+        <v>0.7048</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3737</v>
@@ -2248,13 +2248,13 @@
         <v>2.5224</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4186</v>
+        <v>-0.2123</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4105</v>
+        <v>-0.3104</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.008</v>
+        <v>0.0982</v>
       </c>
       <c r="V23" t="n">
         <v>0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.0242</v>
+        <v>-7.8997</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2395</v>
+        <v>-6.1394</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7847</v>
+        <v>-1.7602</v>
       </c>
       <c r="G24" t="n">
         <v>-4.369</v>
@@ -2326,13 +2326,13 @@
         <v>2.3284</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3149</v>
+        <v>-0.1904</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4834</v>
+        <v>-0.3833</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1685</v>
+        <v>0.1929</v>
       </c>
       <c r="V24" t="n">
         <v>-1.788</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.446300000000001</v>
+        <v>-6.778999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.919999999999998</v>
+        <v>-1.92</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.526199999999999</v>
+        <v>-4.8588</v>
       </c>
       <c r="G25" t="n">
         <v>-5.699299999999999</v>
@@ -2377,10 +2377,10 @@
         <v>-3.392300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>8.7521</v>
+        <v>8.752099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>7.917600000000002</v>
+        <v>7.9176</v>
       </c>
       <c r="L25" t="n">
         <v>0.8344</v>
@@ -2404,13 +2404,13 @@
         <v>17.4629</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.1516</v>
+        <v>-2.4843</v>
       </c>
       <c r="T25" t="n">
         <v>-2.4733</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6783000000000002</v>
+        <v>-0.01100000000000009</v>
       </c>
       <c r="V25" t="n">
         <v>-1.506</v>
